--- a/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/screenshot-map.xlsx
+++ b/plugins/xiaohongshu-reimbursement-workflow/skills/xiaohongshu-reimbursement-workflow/assets/templates/xiaohongshu/screenshot-map.xlsx
@@ -9,12 +9,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="9">
     <x:numFmt numFmtId="200" formatCode="mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0.000"/>
     <x:numFmt numFmtId="204" formatCode="0.0"/>
+    <x:numFmt numFmtId="210" formatCode="0"/>
+    <x:numFmt numFmtId="211" formatCode="0.0"/>
+    <x:numFmt numFmtId="212" formatCode="0.00"/>
+    <x:numFmt numFmtId="213" formatCode="0.000"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -129,7 +133,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="113">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -151,22 +155,22 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -181,7 +185,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="210" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -374,6 +378,39 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="212" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -576,61 +613,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="13" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="48" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="42" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="6" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">日期</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">支出人/主体</t>
+          <t>支出人/主体</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">项目</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">金额</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">备注</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">图1</t>
+          <t>图1</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">图2</t>
+          <t>图2</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">图3</t>
+          <t>图3</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="172.5" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -641,5 +677,6 @@
       <c r="H2" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="0"/>
 </worksheet>
 </file>